--- a/Paket_8_Matematika_TKA_SD.xlsx
+++ b/Paket_8_Matematika_TKA_SD.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Paket 8 Matematika" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -471,27 +471,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[Paket 8] Soal Matematika 1: contoh soal numerasi sederhana.</t>
+          <t>Sekolah SD Merdeka membeli 25 dus pensil standar untuk persiapan ulangan tengah semester. Setiap dus berisi 144 batang pensil. Pensil tersebut akan dibagikan merata kepada 900 siswa. Berapa batang pensil yang diterima setiap siswa?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. 3 batang</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. 4 batang</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. 5 batang</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. 6 batang</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -502,7 +502,11 @@
       <c r="H2" t="n">
         <v>60</v>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -512,27 +516,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[Paket 8] Soal Matematika 2: contoh soal numerasi sederhana.</t>
+          <t>Suhu rata-rata permukaan bumi adalah 15°C. Pada musim dingin, suhu di daerah kutub utara bisa turun hingga 42°C di bawah suhu rata-rata permukaan bumi. Berapakah suhu di daerah kutub utara pada musim dingin tersebut?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. -27°C</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. -25°C</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. 27°C</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. 57°C</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -543,7 +547,11 @@
       <c r="H3" t="n">
         <v>60</v>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -553,27 +561,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[Paket 8] Soal Matematika 3: contoh soal numerasi sederhana.</t>
+          <t>Hasil dari (3 1/2 + 4 2/3) × (5 1/2 - 2 1/4) adalah...</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. 40 1/12</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. 41 5/12</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. 42 1/4</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. 43 7/12</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -584,7 +592,11 @@
       <c r="H4" t="n">
         <v>60</v>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -594,27 +606,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[Paket 8] Soal Matematika 4: contoh soal numerasi sederhana.</t>
+          <t>Hasil dari (2 1/4 + 3 2/3) × (4 1/2 - 1 3/4) adalah...</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. 21 11/12</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. 22 7/12</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. 23 5/12</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. 24 1/12</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -625,7 +637,11 @@
       <c r="H5" t="n">
         <v>60</v>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -635,27 +651,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[Paket 8] Soal Matematika 5: contoh soal numerasi sederhana.</t>
+          <t>Hasil dari (2/3 + 3/4) : (5/6 - 1/2) adalah...</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. 1 7/12</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. 1 11/12</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. 2 1/12</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. 2 5/12</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -666,7 +682,11 @@
       <c r="H6" t="n">
         <v>60</v>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -676,27 +696,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[Paket 8] Soal Matematika 6: contoh soal numerasi sederhana.</t>
+          <t>Ibu memiliki 5 kg tepung terigu. Sebanyak 1 3/4 kg digunakan untuk membuat bolu dan 1 1/2 kg digunakan untuk membuat donat. Berapa kilogram sisa tepung terigu Ibu?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. 1 1/4 kg</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. 1 3/4 kg</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. 2 1/4 kg</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. 2 3/4 kg</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -707,7 +727,11 @@
       <c r="H7" t="n">
         <v>60</v>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -717,27 +741,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[Paket 8] Soal Matematika 7: contoh soal numerasi sederhana.</t>
+          <t>Dalam upacara bendera, siswa berbaris dalam beberapa barisan. Jika dibentuk barisan 12 siswa per baris, sisa 5 siswa. Jika dibentuk barisan 15 siswa per baris, sisa 8 siswa. Jika total siswa kurang dari 100 orang, berapakah jumlah siswa yang mengikuti upacara?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. 53 orang</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. 58 orang</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. 68 orang</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. 77 orang</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -748,17 +772,21 @@
       <c r="H8" t="n">
         <v>60</v>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[Paket 8] Soal Matematika 8: contoh soal numerasi sederhana.</t>
+          <t>Koperasi sekolah memiliki 84 buah apel, 108 buah jeruk, dan 132 buah pir yang akan dikemas ke dalam beberapa kotak buah-buahan dengan isi yang sama banyak tanpa sisa. Manakah pernyataan berikut yang BENAR? (Jawaban benar lebih dari satu) ☐ A. FPB dari 84, 108, dan 132 adalah 12 ☐ B. Jumlah kotak buah terbanyak yang dapat dibentuk adalah 12 kotak ☐ C. Setiap kotak berisi 7 apel, 9 jeruk, dan 11 pir ☐ D. Total buah di setiap kotak adalah 28 buah [Pilihan Ganda Kompleks: Jawaban benar lebih dari satu]</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -789,17 +817,21 @@
       <c r="H9" t="n">
         <v>60</v>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[Paket 8] Soal Matematika 9: contoh soal numerasi sederhana.</t>
+          <t>Koperasi sekolah memiliki 84 buah apel, 108 buah jeruk, dan 132 buah pir yang akan dikemas ke dalam beberapa kotak buah-buahan dengan isi yang sama banyak tanpa sisa. Manakah pernyataan berikut yang BENAR? (Jawaban benar lebih dari satu) ☐ A. FPB dari 84, 108, dan 132 adalah 12 ☐ B. Jumlah kotak buah terbanyak yang dapat dibentuk adalah 12 kotak ☐ C. Setiap kotak berisi 6 apel, 9 jeruk, dan 10 pir ☐ D. Total buah di setiap kotak adalah 27 buah [Pilihan Ganda Kompleks: Jawaban benar lebih dari satu]</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -830,7 +862,11 @@
       <c r="H10" t="n">
         <v>60</v>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -840,27 +876,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[Paket 8] Soal Matematika 10: contoh soal numerasi sederhana.</t>
+          <t>Seorang arsitek membuat denah rumah dengan skala 1 : 150. Pada denah, lebar kamar tidur utama terukur 4 cm. Jika biaya pemasangan keramik lantai Rp120.000 per m², berapakah biaya pemasangan keramik untuk kamar tidur utama tersebut?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. Rp4.320.000</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. Rp4.500.000</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. Rp4.800.000</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. Rp5.400.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -871,7 +907,11 @@
       <c r="H11" t="n">
         <v>60</v>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -881,27 +921,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>[Paket 8] Soal Matematika 11: contoh soal numerasi sederhana.</t>
+          <t>Sebidang tanah kosong berbentuk persegi panjang diukur menggunakan pita meteran. Pada gambar rancangan arsitek dengan skala 1 : 200, panjang tanah 12 cm dan lebar 8 cm. Berapakah luas sebenarnya tanah tersebut?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. 3.840 m²</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. 4.800 m²</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. 5.760 m²</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. 7.680 m²</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -912,7 +952,11 @@
       <c r="H12" t="n">
         <v>60</v>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -922,27 +966,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[Paket 8] Soal Matematika 12: contoh soal numerasi sederhana.</t>
+          <t>Pada gambar rancangan rumah dengan skala 1 : 200, ukuran kamar mandi adalah 3 cm × 2,5 cm. Luas sebenarnya kamar mandi tersebut adalah...</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. 3 m²</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. 2,5 m²</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. 2 m²</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. 1,5 m²</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -953,7 +997,11 @@
       <c r="H13" t="n">
         <v>60</v>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -963,27 +1011,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[Paket 8] Soal Matematika 13: contoh soal numerasi sederhana.</t>
+          <t>Sebidang tanah berbentuk persegi panjang digambar pada skala 1 : 100. Pada gambar, panjang tanah 15 cm dan lebar 8 cm. Luas sebenarnya tanah tersebut adalah...</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. 1.200 m²</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. 1.080 m²</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. 960 m²</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. 840 m²</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -994,7 +1042,11 @@
       <c r="H14" t="n">
         <v>60</v>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1004,27 +1056,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[Paket 8] Soal Matematika 14: contoh soal numerasi sederhana.</t>
+          <t>Sebuah model mobil skala 1 : 50 memiliki panjang badan 8,4 cm. Jika mobil aslinya memiliki lebar 1,8 meter, berapakah lebar model mobil tersebut dalam cm?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. 3,6 cm</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. 4,2 cm</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. 4,8 cm</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. 5,4 cm</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1035,17 +1087,21 @@
       <c r="H15" t="n">
         <v>60</v>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>[Paket 8] Soal Matematika 15: contoh soal numerasi sederhana.</t>
+          <t>Pak Budi menabung uang sebesar Rp2.000.000 di bank dengan suku bunga majemuk 12% per tahun. Uang tersebut tidak diambil selama 2 tahun. Tentukan kebenaran dari pernyataan-pernyataan berikut! (Gunakan rumus bunga majemuk: A = M(1 + i)ⁿ) [Pilihan Ganda Kompleks: Kategori Benar / Salah]</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1076,7 +1132,11 @@
       <c r="H16" t="n">
         <v>60</v>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1086,27 +1146,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>[Paket 8] Soal Matematika 16: contoh soal numerasi sederhana.</t>
+          <t>Kereta api berangkat dari Stasiun A menuju Stasiun B yang berjarak 360 km. Kecepatan rata-rata kereta api 80 km/jam. Jika kereta berangkat pukul 06.30 WIB dan berhenti di Stasiun Transit selama 15 menit, pada pukul berapakah kereta tiba di Stasiun B?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. 10.45 WIB</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. 11.00 WIB</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. 11.15 WIB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. 11.30 WIB</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1117,7 +1177,11 @@
       <c r="H17" t="n">
         <v>60</v>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1127,27 +1191,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>[Paket 8] Soal Matematika 17: contoh soal numerasi sederhana.</t>
+          <t>Seorang programmer menulis kode program dalam 3 sesi kerja: • Sesi 1: 2 jam 45 menit • Sesi 2: 1 jam 50 menit • Sesi 3: 3 jam 35 menit Total waktu yang dibutuhkan programmer tersebut adalah...</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. 7 jam 10 menit</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. 7 jam 50 menit</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. 8 jam 10 menit</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. 8 jam 50 menit</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1158,7 +1222,11 @@
       <c r="H18" t="n">
         <v>60</v>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1168,27 +1236,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[Paket 8] Soal Matematika 18: contoh soal numerasi sederhana.</t>
+          <t>Sebuah truk muatan berat bermuatan pasir sebanyak 8.500 kg. Sebagian pasir dibongkar di proyek A sebanyak 2,8 ton, dan dibongkar di proyek B sebanyak 15 kuintal. Berapa kilogram sisa pasir di atas truk?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. 3.700 kg</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. 4.200 kg</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. 4.500 kg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. 4.800 kg</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1199,7 +1267,11 @@
       <c r="H19" t="n">
         <v>60</v>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1209,27 +1281,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[Paket 8] Soal Matematika 19: contoh soal numerasi sederhana.</t>
+          <t>Sebuah bak mandi berbentuk balok ukuran 120 cm × 60 cm × 50 cm diisi air melalui kran dengan debit 30 liter/menit. Jika bak awalnya kosong, berapa menit waktu yang dibutuhkan agar air mencapai ketinggian 30 cm?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. 60 menit</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. 72 menit</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. 84 menit</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. 96 menit</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1240,7 +1312,11 @@
       <c r="H20" t="n">
         <v>60</v>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1250,27 +1326,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>[Paket 8] Soal Matematika 20: contoh soal numerasi sederhana.</t>
+          <t>Sebuah bak mandi berbentuk balok ukuran 150 cm × 80 cm × 60 cm diisi air melalui kran dengan debit 40 liter/menit. Jika bak awalnya kosong, berapa menit waktu yang dibutuhkan agar air mencapai ketinggian 40 cm?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. 100 menit</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. 110 menit</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. 120 menit</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. 130 menit</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1281,7 +1357,11 @@
       <c r="H21" t="n">
         <v>60</v>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
